--- a/Assets/StellaStair/GameData/UnitAttackRanges.xlsx
+++ b/Assets/StellaStair/GameData/UnitAttackRanges.xlsx
@@ -17,9 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="59">
   <si>
-    <t>Target Range IDs</t>
-  </si>
-  <si>
     <t>Effect Range IDs</t>
   </si>
   <si>
@@ -29,25 +26,10 @@
     <t>Range</t>
   </si>
   <si>
-    <t>blank empty / 0 red / 1 yellow center</t>
+    <t>Target Range IDs</t>
   </si>
   <si>
-    <t>AttackMode</t>
-  </si>
-  <si>
-    <t>TargetRangeId</t>
-  </si>
-  <si>
-    <t>Target 1</t>
-  </si>
-  <si>
-    <t>EffectRangeId</t>
-  </si>
-  <si>
-    <t>Knight</t>
-  </si>
-  <si>
-    <t>Effect 1</t>
+    <t>blank empty / 0 red / 1 yellow center</t>
   </si>
   <si>
     <t>RangeId</t>
@@ -56,7 +38,7 @@
     <t>Row</t>
   </si>
   <si>
-    <t>Default</t>
+    <t>AttackMode</t>
   </si>
   <si>
     <t>C01</t>
@@ -65,22 +47,34 @@
     <t>C02</t>
   </si>
   <si>
-    <t>1</t>
+    <t>Effect 1</t>
+  </si>
+  <si>
+    <t>TargetRangeId</t>
+  </si>
+  <si>
+    <t>EffectRangeId</t>
+  </si>
+  <si>
+    <t>Target 1</t>
   </si>
   <si>
     <t>C03</t>
   </si>
   <si>
-    <t>C04</t>
+    <t>Knight</t>
   </si>
   <si>
-    <t>Thrust</t>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>C04</t>
   </si>
   <si>
     <t>C05</t>
   </si>
   <si>
-    <t>5</t>
+    <t>1</t>
   </si>
   <si>
     <t>C06</t>
@@ -89,13 +83,13 @@
     <t>C07</t>
   </si>
   <si>
-    <t>Archer</t>
+    <t>Thrust</t>
   </si>
   <si>
     <t>C08</t>
   </si>
   <si>
-    <t>2</t>
+    <t>5</t>
   </si>
   <si>
     <t>C09</t>
@@ -104,40 +98,46 @@
     <t>C10</t>
   </si>
   <si>
+    <t>Archer</t>
+  </si>
+  <si>
     <t>C11</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C13</t>
   </si>
   <si>
     <t>PiercingArrow</t>
   </si>
   <si>
-    <t>C12</t>
+    <t>C14</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>C13</t>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>Target</t>
   </si>
   <si>
     <t>BowStrike</t>
   </si>
   <si>
-    <t>C14</t>
-  </si>
-  <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>C15</t>
   </si>
   <si>
     <t>Harpoon</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>Target</t>
   </si>
   <si>
     <t>Wizard</t>
@@ -158,16 +158,16 @@
     <t>0</t>
   </si>
   <si>
+    <t>Effect 2</t>
+  </si>
+  <si>
     <t>Target 2</t>
   </si>
   <si>
-    <t>Effect 2</t>
+    <t>Effect 3</t>
   </si>
   <si>
     <t>Target 3</t>
-  </si>
-  <si>
-    <t>Effect 3</t>
   </si>
   <si>
     <t>Target 4</t>
@@ -216,6 +216,11 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF111827"/>
       <name val="Calibri"/>
     </font>
@@ -228,11 +233,6 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FF111827"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -485,15 +485,15 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="5" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -534,11 +534,11 @@
     <xf borderId="10" fillId="5" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="5" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -813,16 +813,16 @@
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="21.0" customHeight="1"/>
     <row r="3" ht="21.0" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
+      <c r="A3" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="21.0" customHeight="1">
@@ -1101,8 +1101,8 @@
     <row r="19" ht="21.0" customHeight="1"/>
     <row r="20" ht="21.0" customHeight="1"/>
     <row r="21" ht="21.0" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>47</v>
+      <c r="A21" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22" ht="21.0" customHeight="1">
@@ -1389,8 +1389,8 @@
     <row r="37" ht="21.0" customHeight="1"/>
     <row r="38" ht="21.0" customHeight="1"/>
     <row r="39" ht="21.0" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>49</v>
+      <c r="A39" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="40" ht="21.0" customHeight="1">
@@ -1705,7 +1705,7 @@
     <row r="55" ht="21.0" customHeight="1"/>
     <row r="56" ht="21.0" customHeight="1"/>
     <row r="57" ht="21.0" customHeight="1">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2745,7 +2745,9 @@
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
       <c r="E118" s="14"/>
-      <c r="F118" s="14"/>
+      <c r="F118" s="16">
+        <v>0.0</v>
+      </c>
       <c r="G118" s="16">
         <v>0.0</v>
       </c>
@@ -2755,7 +2757,9 @@
       <c r="I118" s="16">
         <v>0.0</v>
       </c>
-      <c r="J118" s="14"/>
+      <c r="J118" s="16">
+        <v>0.0</v>
+      </c>
       <c r="K118" s="14"/>
       <c r="L118" s="14"/>
       <c r="M118" s="14"/>
@@ -2768,7 +2772,9 @@
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
       <c r="E119" s="14"/>
-      <c r="F119" s="14"/>
+      <c r="F119" s="16">
+        <v>0.0</v>
+      </c>
       <c r="G119" s="16">
         <v>0.0</v>
       </c>
@@ -2778,7 +2784,9 @@
       <c r="I119" s="16">
         <v>0.0</v>
       </c>
-      <c r="J119" s="14"/>
+      <c r="J119" s="16">
+        <v>0.0</v>
+      </c>
       <c r="K119" s="14"/>
       <c r="L119" s="14"/>
       <c r="M119" s="14"/>
@@ -2791,7 +2799,9 @@
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
-      <c r="F120" s="14"/>
+      <c r="F120" s="16">
+        <v>0.0</v>
+      </c>
       <c r="G120" s="16">
         <v>0.0</v>
       </c>
@@ -2801,7 +2811,9 @@
       <c r="I120" s="16">
         <v>0.0</v>
       </c>
-      <c r="J120" s="14"/>
+      <c r="J120" s="16">
+        <v>0.0</v>
+      </c>
       <c r="K120" s="14"/>
       <c r="L120" s="14"/>
       <c r="M120" s="14"/>
@@ -4716,15 +4728,15 @@
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="21.0" customHeight="1"/>
     <row r="3" ht="21.0" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4988,8 +5000,8 @@
     <row r="19" ht="21.0" customHeight="1"/>
     <row r="20" ht="21.0" customHeight="1"/>
     <row r="21" ht="21.0" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>48</v>
+      <c r="A21" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" ht="21.0" customHeight="1">
@@ -5257,7 +5269,7 @@
     <row r="38" ht="21.0" customHeight="1"/>
     <row r="39" ht="21.0" customHeight="1">
       <c r="A39" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -6514,101 +6526,101 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" s="10">
         <v>1.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -6616,13 +6628,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -6630,13 +6642,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -6644,13 +6656,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -7653,67 +7665,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="8">
         <v>1.0</v>
@@ -7736,10 +7748,10 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="8">
         <v>2.0</v>
@@ -7762,10 +7774,10 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="8">
         <v>3.0</v>
@@ -7788,10 +7800,10 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="8">
         <v>4.0</v>
@@ -7814,10 +7826,10 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="8">
         <v>5.0</v>
@@ -7840,10 +7852,10 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8">
         <v>6.0</v>
@@ -7866,10 +7878,10 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" s="8">
         <v>7.0</v>
@@ -7894,10 +7906,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8">
         <v>8.0</v>
@@ -7912,7 +7924,7 @@
         <v>46</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>46</v>
@@ -7926,10 +7938,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" s="8">
         <v>9.0</v>
@@ -7954,10 +7966,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8">
         <v>10.0</v>
@@ -7980,10 +7992,10 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8">
         <v>11.0</v>
@@ -8006,10 +8018,10 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8">
         <v>12.0</v>
@@ -8032,10 +8044,10 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C14" s="8">
         <v>13.0</v>
@@ -8058,10 +8070,10 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15" s="8">
         <v>14.0</v>
@@ -8084,10 +8096,10 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16" s="8">
         <v>15.0</v>
@@ -8110,10 +8122,10 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C17" s="8">
         <v>1.0</v>
@@ -8136,10 +8148,10 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" s="8">
         <v>2.0</v>
@@ -8162,10 +8174,10 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C19" s="8">
         <v>3.0</v>
@@ -8188,10 +8200,10 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C20" s="8">
         <v>4.0</v>
@@ -8214,10 +8226,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="8">
         <v>5.0</v>
@@ -8240,10 +8252,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C22" s="8">
         <v>6.0</v>
@@ -8266,10 +8278,10 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C23" s="8">
         <v>7.0</v>
@@ -8292,10 +8304,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C24" s="8">
         <v>8.0</v>
@@ -8314,7 +8326,7 @@
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8" t="s">
@@ -8332,10 +8344,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C25" s="8">
         <v>9.0</v>
@@ -8358,10 +8370,10 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26" s="8">
         <v>10.0</v>
@@ -8384,10 +8396,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C27" s="8">
         <v>11.0</v>
@@ -8410,10 +8422,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C28" s="8">
         <v>12.0</v>
@@ -8436,10 +8448,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C29" s="8">
         <v>13.0</v>
@@ -8462,10 +8474,10 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C30" s="8">
         <v>14.0</v>
@@ -8488,10 +8500,10 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C31" s="8">
         <v>15.0</v>
@@ -8514,7 +8526,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>42</v>
@@ -8540,7 +8552,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>42</v>
@@ -8566,7 +8578,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>42</v>
@@ -8592,7 +8604,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>42</v>
@@ -8618,7 +8630,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>42</v>
@@ -8644,7 +8656,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>42</v>
@@ -8672,7 +8684,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>42</v>
@@ -8704,7 +8716,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>42</v>
@@ -8724,7 +8736,7 @@
         <v>46</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>46</v>
@@ -8740,7 +8752,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>42</v>
@@ -8772,7 +8784,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>42</v>
@@ -8800,7 +8812,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>42</v>
@@ -8826,7 +8838,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>42</v>
@@ -8852,7 +8864,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>42</v>
@@ -8878,7 +8890,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>42</v>
@@ -8904,7 +8916,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>42</v>
@@ -8930,7 +8942,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>45</v>
@@ -8956,7 +8968,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>45</v>
@@ -8982,7 +8994,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>45</v>
@@ -9008,7 +9020,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>45</v>
@@ -9034,7 +9046,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>45</v>
@@ -9060,7 +9072,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>45</v>
@@ -9086,7 +9098,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>45</v>
@@ -9112,7 +9124,7 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>45</v>
@@ -9134,7 +9146,7 @@
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
@@ -9152,7 +9164,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>45</v>
@@ -9178,7 +9190,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>45</v>
@@ -9204,7 +9216,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>45</v>
@@ -9230,7 +9242,7 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>45</v>
@@ -9256,7 +9268,7 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>45</v>
@@ -9282,7 +9294,7 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>45</v>
@@ -9308,7 +9320,7 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>45</v>
@@ -9337,7 +9349,7 @@
         <v>53</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C62" s="8">
         <v>1.0</v>
@@ -9363,7 +9375,7 @@
         <v>53</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C63" s="8">
         <v>2.0</v>
@@ -9389,7 +9401,7 @@
         <v>53</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C64" s="8">
         <v>3.0</v>
@@ -9415,7 +9427,7 @@
         <v>53</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C65" s="8">
         <v>4.0</v>
@@ -9441,7 +9453,7 @@
         <v>53</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C66" s="8">
         <v>5.0</v>
@@ -9467,7 +9479,7 @@
         <v>53</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C67" s="8">
         <v>6.0</v>
@@ -9493,7 +9505,7 @@
         <v>53</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C68" s="8">
         <v>7.0</v>
@@ -9519,7 +9531,7 @@
         <v>53</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C69" s="8">
         <v>8.0</v>
@@ -9532,7 +9544,7 @@
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L69" s="8"/>
       <c r="M69" s="8"/>
@@ -9547,7 +9559,7 @@
         <v>53</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C70" s="8">
         <v>9.0</v>
@@ -9573,7 +9585,7 @@
         <v>53</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C71" s="8">
         <v>10.0</v>
@@ -9599,7 +9611,7 @@
         <v>53</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C72" s="8">
         <v>11.0</v>
@@ -9625,7 +9637,7 @@
         <v>53</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C73" s="8">
         <v>12.0</v>
@@ -9651,7 +9663,7 @@
         <v>53</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C74" s="8">
         <v>13.0</v>
@@ -9677,7 +9689,7 @@
         <v>53</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C75" s="8">
         <v>14.0</v>
@@ -9703,7 +9715,7 @@
         <v>53</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C76" s="8">
         <v>15.0</v>
@@ -9729,7 +9741,7 @@
         <v>53</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C77" s="8">
         <v>1.0</v>
@@ -9755,7 +9767,7 @@
         <v>53</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C78" s="8">
         <v>2.0</v>
@@ -9781,7 +9793,7 @@
         <v>53</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C79" s="8">
         <v>3.0</v>
@@ -9807,7 +9819,7 @@
         <v>53</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C80" s="8">
         <v>4.0</v>
@@ -9833,7 +9845,7 @@
         <v>53</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C81" s="8">
         <v>5.0</v>
@@ -9859,7 +9871,7 @@
         <v>53</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C82" s="8">
         <v>6.0</v>
@@ -9885,7 +9897,7 @@
         <v>53</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C83" s="8">
         <v>7.0</v>
@@ -9911,7 +9923,7 @@
         <v>53</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C84" s="8">
         <v>8.0</v>
@@ -9926,7 +9938,7 @@
         <v>46</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L84" s="8" t="s">
         <v>46</v>
@@ -9943,7 +9955,7 @@
         <v>53</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C85" s="8">
         <v>9.0</v>
@@ -9969,7 +9981,7 @@
         <v>53</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C86" s="8">
         <v>10.0</v>
@@ -9995,7 +10007,7 @@
         <v>53</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C87" s="8">
         <v>11.0</v>
@@ -10021,7 +10033,7 @@
         <v>53</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C88" s="8">
         <v>12.0</v>
@@ -10047,7 +10059,7 @@
         <v>53</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C89" s="8">
         <v>13.0</v>
@@ -10073,7 +10085,7 @@
         <v>53</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C90" s="8">
         <v>14.0</v>
@@ -10099,7 +10111,7 @@
         <v>53</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C91" s="8">
         <v>15.0</v>
@@ -11050,36 +11062,36 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>8</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -11090,7 +11102,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -11098,10 +11110,10 @@
         <v>43</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -11112,7 +11124,7 @@
         <v>45</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
